--- a/AAII_Financials/Quarterly/BLCO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BLCO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="92">
   <si>
     <t>BLCO</t>
   </si>
@@ -656,110 +656,111 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
@@ -769,77 +770,80 @@
       <c r="AB7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>1394000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1244000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1405000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1281000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1278000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1137000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1280000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1196000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1216000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1099000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1173000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1007000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1035000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>931000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>996000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>942000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>941000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>889000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1001000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2764000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>944000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2468000</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z8" s="3" t="s">
         <v>3</v>
       </c>
@@ -849,77 +853,80 @@
       <c r="AB8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>527000</v>
+      </c>
+      <c r="E9" s="3">
         <v>483000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>533000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>510000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>525000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>482000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>501000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>464000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>483000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>424000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>461000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>392000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>417000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>372000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>420000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>372000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>379000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>348000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>403000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1064000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>370000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>915000</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
@@ -929,77 +936,80 @@
       <c r="AB9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>867000</v>
+      </c>
+      <c r="E10" s="3">
         <v>761000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>872000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>771000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>753000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>655000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>779000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>732000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>733000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>675000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>712000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>615000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>618000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>559000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>576000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>570000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>562000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>541000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>598000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1700000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>574000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1553000</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1009,8 +1019,11 @@
       <c r="AB10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1039,77 +1052,78 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>114000</v>
+      </c>
+      <c r="E12" s="3">
         <v>101000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>94000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>95000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>96000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>86000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>93000</v>
-      </c>
-      <c r="J12" s="3">
-        <v>84000</v>
       </c>
       <c r="K12" s="3">
         <v>84000</v>
       </c>
       <c r="L12" s="3">
+        <v>84000</v>
+      </c>
+      <c r="M12" s="3">
         <v>82000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>80000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>82000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>85000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>77000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>78000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>77000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>75000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>77000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>70000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>201000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>66000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>187000</v>
       </c>
-      <c r="Y12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1119,8 +1133,11 @@
       <c r="AB12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1199,77 +1216,80 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E14" s="3">
         <v>27000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>46000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-18000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>31000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>22000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-1000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>22000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>14000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>9000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>20000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>28000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>17000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>9000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>4000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>6000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-1000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>2000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>1000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>12000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>1000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>3000</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1279,8 +1299,11 @@
       <c r="AB14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1288,68 +1311,68 @@
         <v>57000</v>
       </c>
       <c r="E15" s="3">
+        <v>57000</v>
+      </c>
+      <c r="F15" s="3">
         <v>56000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>68000</v>
-      </c>
-      <c r="G15" s="3">
-        <v>67000</v>
       </c>
       <c r="H15" s="3">
         <v>67000</v>
       </c>
       <c r="I15" s="3">
+        <v>67000</v>
+      </c>
+      <c r="J15" s="3">
         <v>68000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>72000</v>
-      </c>
-      <c r="K15" s="3">
-        <v>74000</v>
       </c>
       <c r="L15" s="3">
         <v>74000</v>
       </c>
       <c r="M15" s="3">
+        <v>74000</v>
+      </c>
+      <c r="N15" s="3">
         <v>80000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>47000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>56000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>57000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>56000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>59000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>64000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>65000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>67000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>225000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>76000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>247000</v>
       </c>
-      <c r="Y15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1359,8 +1382,11 @@
       <c r="AB15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1386,77 +1412,78 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1286000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1185000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1247000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1201000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1267000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1198000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1194000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1131000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1176000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1084000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1104000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>939000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>975000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>924000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>945000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>896000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>885000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>835000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>909000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2527000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>861000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2291000</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1466,77 +1493,80 @@
       <c r="AB17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>108000</v>
+      </c>
+      <c r="E18" s="3">
         <v>59000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>158000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>80000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>11000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-61000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>86000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>65000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>40000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>15000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>69000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>68000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>60000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>7000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>51000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>46000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>56000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>54000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>92000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>237000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>83000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>177000</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1546,8 +1576,11 @@
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1576,77 +1609,78 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E20" s="3">
         <v>3000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>4000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>3000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>6000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>4000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>5000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>3000</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>10000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>3000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>9000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>6000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-6000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>8000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>15000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-5000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-6000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-5000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>20000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>10000</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1656,77 +1690,80 @@
       <c r="AB20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>160000</v>
+      </c>
+      <c r="E21" s="3">
         <v>113000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>210000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>145000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>76000</v>
       </c>
-      <c r="H21" s="3">
-        <v>0</v>
-      </c>
       <c r="I21" s="3">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3">
         <v>150000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>132000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>111000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>89000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>139000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>112000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>107000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>58000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>138000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>147000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>169000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>144000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>186000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>547000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>209000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>523000</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1736,65 +1773,68 @@
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>93000</v>
+      </c>
+      <c r="E22" s="3">
         <v>97000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>98000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>101000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>128000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>94000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>98000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>100000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>102000</v>
-      </c>
-      <c r="L22" s="3">
-        <v>99000</v>
       </c>
       <c r="M22" s="3">
         <v>99000</v>
       </c>
       <c r="N22" s="3">
+        <v>99000</v>
+      </c>
+      <c r="O22" s="3">
         <v>76000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>58000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>50000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>47000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>35000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>44000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>20000</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1807,8 +1847,8 @@
       <c r="Y22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z22" s="3">
-        <v>0</v>
+      <c r="Z22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA22" s="3">
         <v>0</v>
@@ -1816,77 +1856,80 @@
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-64000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>13000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-3000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-147000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-180000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-10000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-58000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-76000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-90000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-57000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-35000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-19000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-55000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>19000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>27000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>29000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>86000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>232000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>103000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>187000</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1896,77 +1939,80 @@
       <c r="AB23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E24" s="3">
         <v>6000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>71000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>22000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-89000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>31000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-8000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-66000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>72000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>73000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-6000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>45000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>10000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>33000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-2000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>34000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>20000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>6000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>32000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>93000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>311000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1976,8 +2022,11 @@
       <c r="AB24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2056,77 +2105,80 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-70000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-58000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-25000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-58000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-211000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>8000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-148000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-163000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-51000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-80000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-29000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-88000</v>
       </c>
-      <c r="Q26" s="3">
-        <v>0</v>
-      </c>
       <c r="R26" s="3">
+        <v>0</v>
+      </c>
+      <c r="S26" s="3">
         <v>-15000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>7000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>23000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>54000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>139000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-208000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>191000</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2136,77 +2188,80 @@
       <c r="AB26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-71000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-58000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-28000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-62000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-212000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-3000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-151000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-167000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-54000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-84000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-32000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-90000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-18000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>5000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>20000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>51000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>131000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-209000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>191000</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2216,8 +2271,11 @@
       <c r="AB27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2296,8 +2354,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2376,8 +2437,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2456,8 +2520,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2536,77 +2603,80 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-3000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-4000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-3000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-6000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-4000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-5000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-3000</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-10000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-3000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-9000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-6000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>6000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-8000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-15000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>5000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>6000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>5000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-20000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-10000</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2616,77 +2686,80 @@
       <c r="AB32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-71000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-58000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-28000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-62000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-212000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-3000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-151000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-167000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-54000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-84000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-32000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-90000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-18000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>5000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>20000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>51000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>131000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-209000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>191000</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2696,8 +2769,11 @@
       <c r="AB33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2776,77 +2852,80 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-71000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-58000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-28000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-62000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-212000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-3000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-151000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-167000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-54000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-84000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-32000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-90000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-18000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>5000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>20000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>51000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>131000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-209000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>191000</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2856,82 +2935,85 @@
       <c r="AB35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2941,8 +3023,11 @@
       <c r="AB38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2971,8 +3056,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3001,71 +3087,72 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>367000</v>
+      </c>
+      <c r="E41" s="3">
         <v>268000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>383000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>310000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>266000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>202000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>305000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>329000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>285000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>315000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>331000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>355000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>384000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>346000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>354000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>287000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>437000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>190000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>174000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>130000</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3081,8 +3168,11 @@
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3161,71 +3251,74 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1168000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1107000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1222000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1094000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1088000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1023000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1032000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>971000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1010000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>960000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>875000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>840000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>870000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>714000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>724000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>685000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>674000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>737000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>721000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>655000</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3241,71 +3334,74 @@
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>999000</v>
+      </c>
+      <c r="E44" s="3">
         <v>977000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>976000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1005000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1051000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1031000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1036000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1119000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1069000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1073000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1028000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>754000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>699000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>697000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>628000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>605000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>606000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>598000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>572000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>606000</v>
       </c>
-      <c r="W44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3321,71 +3417,74 @@
       <c r="AB44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E45" s="3">
         <v>2000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>5000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>8000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>4000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>13000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>4000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>7000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>7000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>8000</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3">
         <v>431000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>282000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>284000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>194000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>168000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>170000</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3401,71 +3500,74 @@
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2922000</v>
+      </c>
+      <c r="E46" s="3">
         <v>2776000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2977000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2855000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2846000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2694000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2788000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2828000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2769000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2743000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2742000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2464000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2315000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2184000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2137000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1859000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2001000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1719000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1635000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1561000</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3481,8 +3583,11 @@
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3525,8 +3630,8 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -3561,71 +3666,74 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1799000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1794000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1922000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1711000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1680000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1581000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1636000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1481000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1430000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1397000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1504000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1284000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1294000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1296000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1300000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1222000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1243000</v>
-      </c>
-      <c r="T48" s="3">
-        <v>1225000</v>
       </c>
       <c r="U48" s="3">
         <v>1225000</v>
       </c>
       <c r="V48" s="3">
+        <v>1225000</v>
+      </c>
+      <c r="W48" s="3">
         <v>1186000</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3641,71 +3749,74 @@
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>7892000</v>
+      </c>
+      <c r="E49" s="3">
         <v>7963000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>8039000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>7985000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>8028000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>7994000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8017000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>7965000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>7975000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8062000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>8164000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>8188000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>6561000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>6553000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>6565000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>6483000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>6624000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>6749000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>6850000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>6928000</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3721,8 +3832,11 @@
       <c r="AB49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3801,8 +3915,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3881,71 +3998,74 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>294000</v>
+      </c>
+      <c r="E52" s="3">
         <v>302000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>150000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>303000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>305000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>295000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>143000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>310000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>249000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>231000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>111000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>212000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>207000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>213000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1142000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1132000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1134000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1214000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1113000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1362000</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3961,8 +4081,11 @@
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4041,71 +4164,74 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>13859000</v>
+      </c>
+      <c r="E54" s="3">
         <v>13780000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>14022000</v>
-      </c>
-      <c r="F54" s="3">
-        <v>13832000</v>
       </c>
       <c r="G54" s="3">
         <v>13832000</v>
       </c>
       <c r="H54" s="3">
+        <v>13832000</v>
+      </c>
+      <c r="I54" s="3">
         <v>13428000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>13469000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>13515000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>13250000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>13293000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>13442000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>13068000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>11315000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>11169000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>11144000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>10696000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>11002000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>10907000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>10823000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>11037000</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4121,8 +4247,11 @@
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4151,8 +4280,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4181,71 +4311,72 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>426000</v>
+      </c>
+      <c r="E57" s="3">
         <v>407000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>388000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>395000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>449000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>427000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>389000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>455000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>405000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>426000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>522000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>364000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>348000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>389000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>370000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>295000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>357000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>251000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>239000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>252000</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4261,31 +4392,34 @@
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>43000</v>
+      </c>
+      <c r="E58" s="3">
         <v>39000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>77000</v>
-      </c>
-      <c r="F58" s="3">
-        <v>28000</v>
       </c>
       <c r="G58" s="3">
         <v>28000</v>
       </c>
       <c r="H58" s="3">
+        <v>28000</v>
+      </c>
+      <c r="I58" s="3">
         <v>40000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>72000</v>
-      </c>
-      <c r="J58" s="3">
-        <v>30000</v>
       </c>
       <c r="K58" s="3">
         <v>30000</v>
@@ -4294,13 +4428,13 @@
         <v>30000</v>
       </c>
       <c r="M58" s="3">
+        <v>30000</v>
+      </c>
+      <c r="N58" s="3">
         <v>57000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>30000</v>
-      </c>
-      <c r="O58" s="3">
-        <v>25000</v>
       </c>
       <c r="P58" s="3">
         <v>25000</v>
@@ -4314,8 +4448,8 @@
       <c r="S58" s="3">
         <v>25000</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
+      <c r="T58" s="3">
+        <v>25000</v>
       </c>
       <c r="U58" s="3" t="s">
         <v>3</v>
@@ -4332,8 +4466,8 @@
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z58" s="3">
-        <v>0</v>
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA58" s="3">
         <v>0</v>
@@ -4341,71 +4475,74 @@
       <c r="AB58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>619000</v>
+      </c>
+      <c r="E59" s="3">
         <v>639000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>528000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>572000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>81000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>392000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>483000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>544000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>443000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>448000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>439000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>492000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>464000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>384000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>901000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>879000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>891000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>841000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>860000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>872000</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4421,71 +4558,74 @@
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1890000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1820000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1920000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1896000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1840000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1726000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1738000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1801000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1676000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1617000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1579000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1386000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1325000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1254000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1296000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1199000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1273000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1092000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1099000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1124000</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4501,65 +4641,68 @@
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5072000</v>
+      </c>
+      <c r="E61" s="3">
         <v>5031000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>5168000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4922000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4931000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4789000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4864000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4599000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4602000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4554000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4619000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4435000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2604000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2508000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2411000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2413000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2417000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2220000</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -4581,71 +4724,74 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>435000</v>
+      </c>
+      <c r="E62" s="3">
         <v>458000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>343000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>500000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>539000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>467000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>254000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>442000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>378000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>379000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>249000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>353000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>342000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>341000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>336000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>289000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>341000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>379000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>322000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>519000</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4661,8 +4807,11 @@
       <c r="AB62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4741,8 +4890,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4821,8 +4973,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4901,71 +5056,74 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7415000</v>
+      </c>
+      <c r="E66" s="3">
         <v>7328000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>7503000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>7332000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7324000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6995000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6925000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6854000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6670000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6564000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6522000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>6185000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4285000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4117000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4111000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3967000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4106000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3767000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1494000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1712000</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4981,8 +5139,11 @@
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5011,8 +5172,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5091,8 +5253,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5171,8 +5336,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5251,8 +5419,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5331,65 +5502,68 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1016000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1002000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-931000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-873000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-845000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-783000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-571000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-568000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-572000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-421000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-254000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-200000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-116000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-84000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>6000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>7000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>25000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>20000</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5402,8 +5576,8 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z72" s="3">
-        <v>0</v>
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA72" s="3">
         <v>0</v>
@@ -5411,8 +5585,11 @@
       <c r="AB72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5491,8 +5668,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5571,8 +5751,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5651,71 +5834,74 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6376000</v>
+      </c>
+      <c r="E76" s="3">
         <v>6379000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6448000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6429000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6440000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6361000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>6473000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6589000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6504000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6659000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6850000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>6817000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>6958000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>6983000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>7033000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>6729000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>6896000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>7140000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>9329000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>9325000</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5731,8 +5917,11 @@
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5811,82 +6000,85 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5896,77 +6088,80 @@
       <c r="AB80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-71000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-58000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-28000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-62000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-212000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-3000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-151000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-167000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-54000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-84000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-32000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-90000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-18000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>5000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>20000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>51000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>131000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-209000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>191000</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5976,8 +6171,11 @@
       <c r="AB81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6006,22 +6204,23 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>40000</v>
+      </c>
+      <c r="E83" s="3">
         <v>39000</v>
-      </c>
-      <c r="E83" s="3">
-        <v>38000</v>
       </c>
       <c r="F83" s="3">
         <v>38000</v>
       </c>
       <c r="G83" s="3">
-        <v>36000</v>
+        <v>38000</v>
       </c>
       <c r="H83" s="3">
         <v>36000</v>
@@ -6030,53 +6229,53 @@
         <v>36000</v>
       </c>
       <c r="J83" s="3">
+        <v>36000</v>
+      </c>
+      <c r="K83" s="3">
         <v>35000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>37000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>34000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>37000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>34000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>98000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>95000</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>93000</v>
       </c>
       <c r="R83" s="3">
         <v>93000</v>
       </c>
       <c r="S83" s="3">
+        <v>93000</v>
+      </c>
+      <c r="T83" s="3">
         <v>98000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>95000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>100000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>315000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>106000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>336000</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6086,8 +6285,11 @@
       <c r="AB83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6166,8 +6368,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6246,8 +6451,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6326,8 +6534,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6406,8 +6617,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6486,77 +6700,80 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>153000</v>
+      </c>
+      <c r="E89" s="3">
         <v>32000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>136000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>137000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>35000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-25000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>22000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>154000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>15000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>41000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>15000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>48000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-24000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-56000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>159000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>27000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>156000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>3000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>162000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>711000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>134000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>388000</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6566,8 +6783,11 @@
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6596,77 +6816,78 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-71000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-76000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-74000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-89000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-110000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-92000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-60000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-72000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-67000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-84000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-33000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-27000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-37000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-50000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-49000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-34000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-42000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-62000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-131000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-75000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-178000</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6676,8 +6897,11 @@
       <c r="AB91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6756,8 +6980,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6836,77 +7063,80 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-87000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-130000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-188000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-61000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-90000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-116000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-185000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-96000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-74000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-57000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-135000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1882000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-28000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-64000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-90000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-49000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-35000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-41000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-81000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-133000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-79000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-177000</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6916,8 +7146,11 @@
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6946,8 +7179,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6990,8 +7224,8 @@
       <c r="P96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -7026,8 +7260,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7106,8 +7343,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7186,8 +7426,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7266,77 +7509,80 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>34000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-20000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>116000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-12000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>90000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>31000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>146000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-20000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>40000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>12000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>86000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1811000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>90000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>91000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-7000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-109000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>145000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>52000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-37000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-675000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-5000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-227000</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7346,77 +7592,80 @@
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E101" s="3">
         <v>9000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-17000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>10000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-4000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-5000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>8000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-9000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-4000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>7000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>21000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-18000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-10000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>21000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-18000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-10000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-1000</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
       <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
         <v>-8000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>9000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>3000</v>
       </c>
-      <c r="Y101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z101" s="3" t="s">
         <v>3</v>
       </c>
@@ -7426,77 +7675,80 @@
       <c r="AB101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>99000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-118000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>65000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>60000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>57000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-101000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-34000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>48000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-23000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-9000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-26000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-32000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>34000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-22000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>83000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-149000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>256000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>13000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>44000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-105000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>59000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-13000</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7504,6 +7756,9 @@
         <v>3</v>
       </c>
       <c r="AB102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
